--- a/4P_Index_Loi_2009-24_Code_Assainissement.xlsx
+++ b/4P_Index_Loi_2009-24_Code_Assainissement.xlsx
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
